--- a/choferes.xlsx
+++ b/choferes.xlsx
@@ -5,21 +5,21 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Control_Combustible\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12210" windowHeight="6105"/>
   </bookViews>
   <sheets>
     <sheet name="choferes" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>Nombre</t>
   </si>
@@ -154,6 +154,9 @@
   </si>
   <si>
     <t>ZURITA LIVIO GONZALO</t>
+  </si>
+  <si>
+    <t>FERNANDEZ ALEJANDRO</t>
   </si>
 </sst>
 </file>
@@ -960,7 +963,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A45"/>
+  <dimension ref="A1:A46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1050,141 +1053,146 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>44</v>
       </c>
     </row>
